--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-imagingstudy.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-imagingstudy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -659,7 +659,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|ServiceRequest|Appointment|AppointmentResponse|Task)
 </t>
   </si>
   <si>
@@ -691,7 +691,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -796,7 +796,7 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure)
 </t>
   </si>
   <si>
@@ -905,7 +905,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|Media|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|Media|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
 </t>
   </si>
   <si>
@@ -1185,7 +1185,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-specimen)
 </t>
   </si>
   <si>
@@ -1268,7 +1268,7 @@
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|CareTeam|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1712,7 +1712,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
